--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488078_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488078_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1015</v>
+        <v>3.6765</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8777</v>
+        <v>1.1438</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2238</v>
+        <v>2.5326</v>
       </c>
       <c r="G2" t="n">
         <v>7.2573</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7029</v>
+        <v>-1.1279</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.057</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6459</v>
+        <v>-0.3371</v>
       </c>
       <c r="V2" t="n">
         <v>2.7009</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6667</v>
+        <v>2.4042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2189</v>
+        <v>3.3601</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4477</v>
+        <v>-0.9559</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7228</v>
+        <v>3.9382</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2948</v>
+        <v>2.0079</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0177</v>
+        <v>1.9303</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0009</v>
+        <v>4.0334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3568</v>
+        <v>2.6635</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3577</v>
+        <v>1.3699</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7237</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6556</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3754</v>
+        <v>0.5604</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5858</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1952</v>
+        <v>-1.0435</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9873</v>
+        <v>-0.3808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7921</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5532</v>
+        <v>1.6899</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>2.6808</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6539</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9301</v>
+        <v>1.8834</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0545</v>
+        <v>0.5869</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1243</v>
+        <v>1.2965</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9382</v>
+        <v>0.7228</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0079</v>
+        <v>-0.2948</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9303</v>
+        <v>1.0177</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0334</v>
+        <v>-0.0009</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6635</v>
+        <v>0.3568</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3699</v>
+        <v>-0.3577</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.7237</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6556</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5604</v>
+        <v>1.3754</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5176</v>
+        <v>-0.9784</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6864</v>
+        <v>-0.6193</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8312</v>
+        <v>-0.3591</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6899</v>
+        <v>0.5532</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6808</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9908</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9053</v>
+        <v>0.9625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9053</v>
+        <v>1.2044</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.2419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9053</v>
+        <v>0.1656</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>0.4316</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6027</v>
+        <v>-0.266</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9053</v>
+        <v>0.0202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>0.0202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6027</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.1455</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.4114</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.6085</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.5855</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8045</v>
+        <v>0.9053</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1025</v>
+        <v>0.9053</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.298</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1656</v>
+        <v>0.9053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4316</v>
+        <v>0.3027</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.266</v>
+        <v>0.6027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0202</v>
+        <v>0.9053</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0202</v>
+        <v>0.3027</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1455</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4114</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7665</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1248</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6417</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2132</v>
+        <v>-0.2727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1037</v>
+        <v>-1.7145</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3169</v>
+        <v>1.4418</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4575</v>
+        <v>0.9654</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9562</v>
+        <v>0.1102</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4137</v>
+        <v>0.8551</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3606</v>
+        <v>-0.5986</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3626</v>
+        <v>-0.6388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7232</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>0.097</v>
+        <v>1.564</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5936</v>
+        <v>0.749</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6905</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9988</v>
+        <v>-0.6434</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2568</v>
+        <v>-0.1248</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.742</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4131</v>
+        <v>-0.3055</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7145</v>
+        <v>-0.2414</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3014</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9654</v>
+        <v>0.4575</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1102</v>
+        <v>-0.9562</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8551</v>
+        <v>1.4137</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5986</v>
+        <v>0.3606</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6388</v>
+        <v>-0.3626</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0.7232</v>
       </c>
       <c r="M8" t="n">
-        <v>1.564</v>
+        <v>0.097</v>
       </c>
       <c r="N8" t="n">
-        <v>0.749</v>
+        <v>-0.5936</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.6905</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5947</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-1.0912</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1248</v>
+        <v>-0.6019</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.659</v>
+        <v>-0.4893</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6132</v>
+        <v>-1.105</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0644</v>
+        <v>0.6569</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6776</v>
+        <v>-1.7619</v>
       </c>
       <c r="G9" t="n">
         <v>1.4496</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5495</v>
+        <v>0.0578</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4333</v>
+        <v>0.0259</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1162</v>
+        <v>0.032</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4142</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9348</v>
+        <v>-1.732</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4962</v>
+        <v>-2.4338</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5614</v>
+        <v>0.7018</v>
       </c>
       <c r="G10" t="n">
         <v>-1.314</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9489</v>
+        <v>-0.7461</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4992</v>
+        <v>-0.4368</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4497</v>
+        <v>-0.3093</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5645</v>
+        <v>-2.9834</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3621</v>
+        <v>-1.809</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2024</v>
+        <v>-1.1743</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1118</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1574</v>
+        <v>-0.5763</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0589</v>
+        <v>-0.388</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2164</v>
+        <v>-0.1883</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4846</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3667</v>
+        <v>-3.6338</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.419</v>
+        <v>-3.8264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0522</v>
+        <v>0.1926</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9602</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0422</v>
+        <v>-0.2249</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3599</v>
+        <v>-0.0476</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3177</v>
+        <v>-0.1773</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4577</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9038</v>
+        <v>-7.0889</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8019</v>
+        <v>-3.9869</v>
       </c>
       <c r="F13" t="n">
         <v>-3.102</v>
@@ -1468,10 +1468,10 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3583</v>
+        <v>-0.5433</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2993</v>
+        <v>-0.4844</v>
       </c>
       <c r="U13" t="n">
         <v>-0.0589</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.6012</v>
+        <v>-7.289399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.4667</v>
+        <v>-6.1546</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1347</v>
+        <v>-1.1349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.7644</v>
+        <v>9.764399999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.0424</v>
+        <v>-7.042400000000001</v>
       </c>
       <c r="I14" t="n">
         <v>16.8071</v>
@@ -1546,10 +1546,10 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.8377</v>
+        <v>-7.525700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.1835</v>
+        <v>-3.8714</v>
       </c>
       <c r="U14" t="n">
         <v>-3.6542</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0733</v>
+        <v>5.9103</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9941</v>
+        <v>4.4661</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0792</v>
+        <v>1.4442</v>
       </c>
       <c r="G15" t="n">
         <v>3.4291</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5341</v>
+        <v>1.3711</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1477</v>
+        <v>0.6197</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3864</v>
+        <v>0.7514</v>
       </c>
       <c r="V15" t="n">
         <v>-0.674</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5741</v>
+        <v>3.9749</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7727</v>
+        <v>2.3465</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8014</v>
+        <v>1.6284</v>
       </c>
       <c r="G16" t="n">
         <v>0.7685999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3842</v>
+        <v>1.785</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0229</v>
+        <v>0.5967</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3613</v>
+        <v>1.1882</v>
       </c>
       <c r="V16" t="n">
         <v>1.6195</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3048</v>
+        <v>3.879</v>
       </c>
       <c r="E17" t="n">
         <v>5.3213</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0165</v>
+        <v>-1.4423</v>
       </c>
       <c r="G17" t="n">
         <v>0.2429</v>
@@ -1780,13 +1780,13 @@
         <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.795</v>
+        <v>1.3693</v>
       </c>
       <c r="T17" t="n">
         <v>0.9363</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8587</v>
+        <v>0.433</v>
       </c>
       <c r="V17" t="n">
         <v>0.4828</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5232</v>
+        <v>1.7096</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5745</v>
+        <v>-2.308</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9487</v>
+        <v>4.0176</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4975</v>
+        <v>-4.4588</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0901</v>
+        <v>-0.5216</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4075</v>
+        <v>-3.9371</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0202</v>
+        <v>-4.0392</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0202</v>
+        <v>-0.6111</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-3.428</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4774</v>
+        <v>-0.4196</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0699</v>
+        <v>0.0895</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4075</v>
+        <v>-0.5091</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3964</v>
+        <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6292</v>
+        <v>1.2187</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5543</v>
+        <v>0.0415</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07489999999999999</v>
+        <v>1.1772</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.9675</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2819</v>
+        <v>1.3299</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0211</v>
+        <v>0.2689</v>
       </c>
       <c r="F19" t="n">
-        <v>4.303</v>
+        <v>1.061</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4588</v>
+        <v>0.4975</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5216</v>
+        <v>0.0901</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.9371</v>
+        <v>0.4075</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.0392</v>
+        <v>0.0202</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6111</v>
+        <v>0.0202</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.428</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4196</v>
+        <v>0.4774</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0895</v>
+        <v>0.0699</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5091</v>
+        <v>0.4075</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9822</v>
+        <v>0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9733</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>0.791</v>
+        <v>0.4359</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6715</v>
+        <v>0.2487</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4625</v>
+        <v>0.1872</v>
       </c>
       <c r="V19" t="n">
-        <v>2.9675</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1753</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="F20" t="n">
         <v>0.1358</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3226</v>
+        <v>-0.3044</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.793</v>
+        <v>-0.696</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4703</v>
+        <v>0.3916</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4584</v>
+        <v>0.518</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1919</v>
+        <v>2.5596</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2665</v>
+        <v>-2.0415</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7365</v>
+        <v>2.139</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4586</v>
+        <v>2.7378</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2779</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7219</v>
+        <v>-1.621</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7333</v>
+        <v>-0.1782</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0114</v>
+        <v>-1.4428</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>0.55</v>
+        <v>0.6947</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9435</v>
+        <v>-0.1282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3936</v>
+        <v>0.823</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4517</v>
+        <v>-1.3017</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5109</v>
+        <v>-1.9967</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0592</v>
+        <v>0.695</v>
       </c>
       <c r="G22" t="n">
-        <v>0.518</v>
+        <v>-3.4584</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5596</v>
+        <v>-2.1919</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0415</v>
+        <v>-1.2665</v>
       </c>
       <c r="J22" t="n">
-        <v>2.139</v>
+        <v>-2.7365</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7378</v>
+        <v>-1.4586</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>-1.2779</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.621</v>
+        <v>-0.7219</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1782</v>
+        <v>-0.7333</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4428</v>
+        <v>0.0114</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4526</v>
+        <v>0.5709</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9432</v>
+        <v>0.7398</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4906</v>
+        <v>-0.1689</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2633</v>
+        <v>-1.7635</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-2.6016</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2789</v>
+        <v>0.838</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5291</v>
+        <v>-3.6861</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3243</v>
+        <v>0.6279</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2048</v>
+        <v>-4.314</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4698</v>
+        <v>-3.1831</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7466</v>
+        <v>0.2087</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7232</v>
+        <v>-3.3918</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9989</v>
+        <v>-0.503</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0709</v>
+        <v>0.4193</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.928</v>
+        <v>-0.9223</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0081</v>
+        <v>1.182</v>
       </c>
       <c r="T23" t="n">
-        <v>0.202</v>
+        <v>0.3149</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1939</v>
+        <v>0.8671</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5441</v>
+        <v>0.1459</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8701</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7646</v>
+        <v>-1.9015</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5184</v>
+        <v>-0.6788</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7538</v>
+        <v>-1.2227</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6861</v>
+        <v>-0.5291</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6279</v>
+        <v>-0.3243</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.314</v>
+        <v>-0.2048</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1831</v>
+        <v>1.4698</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2087</v>
+        <v>0.7466</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3918</v>
+        <v>0.7232</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.503</v>
+        <v>-1.9989</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4193</v>
+        <v>-1.0709</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9223</v>
+        <v>-0.928</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>0.181</v>
+        <v>0.3699</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6019</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7829</v>
+        <v>-0.1377</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1459</v>
+        <v>-1.5441</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1207</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4271</v>
+        <v>-3.4273</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6378</v>
+        <v>-3.0265</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7893</v>
+        <v>-0.4008</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2242</v>
@@ -2404,13 +2404,13 @@
         <v>1.9822</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.52</v>
+        <v>-0.5203</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8736</v>
+        <v>-0.2623</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6465</v>
+        <v>-0.2579</v>
       </c>
       <c r="V25" t="n">
         <v>-0.674</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.601399999999999</v>
+        <v>8.2806</v>
       </c>
       <c r="E26" t="n">
-        <v>1.134599999999999</v>
+        <v>1.134700000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>6.466699999999999</v>
+        <v>7.145799999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.764700000000001</v>
+        <v>-9.764699999999999</v>
       </c>
       <c r="H26" t="n">
         <v>7.0427</v>
@@ -2455,7 +2455,7 @@
         <v>-16.8071</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3692000000000011</v>
+        <v>-0.3692000000000013</v>
       </c>
       <c r="K26" t="n">
         <v>9.931900000000002</v>
@@ -2482,13 +2482,13 @@
         <v>17.84</v>
       </c>
       <c r="S26" t="n">
-        <v>7.837600000000002</v>
+        <v>8.516699999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>3.654100000000001</v>
+        <v>3.6542</v>
       </c>
       <c r="U26" t="n">
-        <v>4.1833</v>
+        <v>4.8626</v>
       </c>
       <c r="V26" t="n">
         <v>1.5993</v>
